--- a/料力榜.xlsx
+++ b/料力榜.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>日期</t>
   </si>
@@ -63,6 +63,9 @@
     <t>评语</t>
   </si>
   <si>
+    <t>视频链接</t>
+  </si>
+  <si>
     <t>EP1</t>
   </si>
   <si>
@@ -75,6 +78,9 @@
     <t>鲜香微辣，值得一试</t>
   </si>
   <si>
+    <t>72 【【料包大王】肉蟹煲料包 真能做出饭店味？ - 料包大王 | 小红书 - 你的生活兴趣社区】 😆 5DFPVdPbUtnXOUJ 😆 https://www.xiaohongshu.com/discovery/item/6aa13f7f000000002503768b?source=webshare&amp;xhsshare=pc_web&amp;xsec_token=AByJMGXU4J2H5oH0YoU9WEXRESOfe84bb9cbYgjF1aGYo=&amp;xsec_source=pc_share</t>
+  </si>
+  <si>
     <t>EP2</t>
   </si>
   <si>
@@ -87,6 +93,9 @@
     <t>清汤寡淡，平平无奇</t>
   </si>
   <si>
+    <t>85 【【料包大王】[盒马]潮汕风味牛骨原汤翻车？ - 料包大王 | 小红书 - 你的生活兴趣社区】 😆 BrRlcs0AE5tG9gt 😆 https://www.xiaohongshu.com/discovery/item/6aa3cfed0000000011036f3e?source=webshare&amp;xhsshare=pc_web&amp;xsec_token=ABT_WH4u8L8neOUQoWl-Ari1hTkodqhE-to0lsWRt9n1U=&amp;xsec_source=pc_share</t>
+  </si>
+  <si>
     <t>EP3</t>
   </si>
   <si>
@@ -96,6 +105,9 @@
     <t>芥味清爽，略欠鲜香</t>
   </si>
   <si>
+    <t>49 【【料包大王】芥末小海鲜捞汁测评 - 料包大王 | 小红书 - 你的生活兴趣社区】 😆 2WMTwRvB4DtG9a0 😆 https://www.xiaohongshu.com/discovery/item/6aa68a5c00000000270151cb?source=webshare&amp;xhsshare=pc_web&amp;xsec_token=ABUWZDZGaKAZJ3VDleOer-J7sC6yv6kjVEvdyNHKhkGDg=&amp;xsec_source=pc_share</t>
+  </si>
+  <si>
     <t>EP4</t>
   </si>
   <si>
@@ -105,6 +117,9 @@
     <t>辣而少香，入味欠佳</t>
   </si>
   <si>
+    <t>36 【【料包大王】云南油焖鸡料包测评 - 料包大王 | 小红书 - 你的生活兴趣社区】 😆 FyvPQRGhdxxh6Nk 😆 https://www.xiaohongshu.com/discovery/item/6aa923d0000000001001fe54?source=webshare&amp;xhsshare=pc_web&amp;xsec_token=AB3ov2gIhESDprneGpbv2PbJQAe8Dd2VNMZyI3Re61XV0=&amp;xsec_source=pc_share</t>
+  </si>
+  <si>
     <t>EP5</t>
   </si>
   <si>
@@ -114,6 +129,9 @@
     <t>酸辣直愣，味略单薄</t>
   </si>
   <si>
+    <t>57 【【料包大王】泰式酸辣凉拌汁测评 - 料包大王 | 小红书 - 你的生活兴趣社区】 😆 ylwX3nr07rkTMHV 😆 https://www.xiaohongshu.com/discovery/item/6aabc07f000000002900f0e6?source=webshare&amp;xhsshare=pc_web&amp;xsec_token=AB5rB28ndyaxfY0RbL0tlfF462bTlA-GzWuGqIapKrl08=&amp;xsec_source=pc_share</t>
+  </si>
+  <si>
     <t>EP6</t>
   </si>
   <si>
@@ -126,6 +144,9 @@
     <t>汤浓味醇，咸味稍重</t>
   </si>
   <si>
+    <t>30 【【料包大王】寿喜烧调味汁测评 - 料包大王 | 小红书 - 你的生活兴趣社区】 😆 tbjMrU0HcaE0v2u 😆 https://www.xiaohongshu.com/discovery/item/6aae597d000000001103b2bb?source=webshare&amp;xhsshare=pc_web&amp;xsec_token=ABc02AacS06bs0KdL8dRB0iNj8euXdnGp6w1zdCOipgIA=&amp;xsec_source=pc_share</t>
+  </si>
+  <si>
     <t>EP7</t>
   </si>
   <si>
@@ -135,6 +156,9 @@
     <t>咸重压味，麻香不足</t>
   </si>
   <si>
+    <t>69 【【料包大王】牛肉麻婆豆腐料包测评 - 料包大王 | 小红书 - 你的生活兴趣社区】 😆 WFGM8XI7k0Xh8TO 😆 https://www.xiaohongshu.com/discovery/item/6ab11246000000003303a805?source=webshare&amp;xhsshare=pc_web&amp;xsec_token=ABrDXYg9qaw-8p4MKgd7jYqyhsJLZiofWfGSHwYLZBkqs=&amp;xsec_source=pc_share</t>
+  </si>
+  <si>
     <t>EP8</t>
   </si>
   <si>
@@ -147,6 +171,9 @@
     <t>酸辣突出，香味稍弱</t>
   </si>
   <si>
+    <t>46 【【料包大王】[山姆]金汤料包测评 - 料包大王 | 小红书 - 你的生活兴趣社区】 😆 BVTZI12vZ8G6iYM 😆 https://www.xiaohongshu.com/discovery/item/6ab3ac090000000018005645?source=webshare&amp;xhsshare=pc_web&amp;xsec_token=AB1V9blKDnuyLvUWgocoBs4KXVJeIBZRkXwcZFywFyFWM=&amp;xsec_source=pc_share</t>
+  </si>
+  <si>
     <t>EP9</t>
   </si>
   <si>
@@ -157,6 +184,9 @@
   </si>
   <si>
     <t>咸香入味，甜度较低</t>
+  </si>
+  <si>
+    <t>1 【【料包大王】日式照烧汁测评 - 料包大王 | 小红书 - 你的生活兴趣社区】 😆 3LWcP1vA1P97Uxu 😆 https://www.xiaohongshu.com/discovery/item/6ab3bf7000000000130180ac?source=webshare&amp;xhsshare=pc_web&amp;xsec_token=AB1V9blKDnuyLvUWgocoBs4ECsZBU8b6AtWdoJwP-mjs8=&amp;xsec_source=pc_share</t>
   </si>
   <si>
     <t>EP10</t>
@@ -819,7 +849,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -854,6 +884,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1167,7 +1200,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:J19"/>
+  <dimension ref="B2:K19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="13.0176991150442" customWidth="1"/>
@@ -1178,7 +1211,7 @@
     <col min="10" max="10" width="21.5752212389381" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="20" customHeight="1" spans="2:10">
+    <row r="2" ht="20" customHeight="1" spans="2:11">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1206,19 +1239,22 @@
       <c r="J2" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="K2" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="2:10">
+    <row r="3" ht="20" customHeight="1" spans="2:11">
       <c r="B3" s="4">
         <v>46274</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="5">
         <v>4.3</v>
@@ -1234,21 +1270,24 @@
         <v>4.13333333333333</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="2:10">
+    <row r="4" ht="20" customHeight="1" spans="2:11">
       <c r="B4" s="4">
         <v>46276</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F4" s="5">
         <v>3.5</v>
@@ -1260,25 +1299,28 @@
         <v>4.5</v>
       </c>
       <c r="I4" s="7">
-        <f t="shared" ref="I4:I11" si="0">AVERAGE(F4:H4)</f>
+        <f t="shared" ref="I4:I13" si="0">AVERAGE(F4:H4)</f>
         <v>3.83333333333333</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" spans="2:10">
+    <row r="5" ht="20" customHeight="1" spans="2:11">
       <c r="B5" s="4">
         <v>46278</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F5" s="5">
         <v>3.7</v>
@@ -1294,21 +1336,24 @@
         <v>3.9</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1" spans="2:10">
+    <row r="6" ht="20" customHeight="1" spans="2:11">
       <c r="B6" s="4">
         <v>46280</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F6" s="5">
         <v>3.4</v>
@@ -1324,21 +1369,24 @@
         <v>3.6</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" spans="2:10">
+    <row r="7" ht="20" customHeight="1" spans="2:11">
       <c r="B7" s="4">
         <v>46282</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F7" s="5">
         <v>3.5</v>
@@ -1354,21 +1402,24 @@
         <v>3.8</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1" spans="2:10">
+    <row r="8" ht="20" customHeight="1" spans="2:11">
       <c r="B8" s="4">
         <v>46284</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F8" s="5">
         <v>4.1</v>
@@ -1384,21 +1435,24 @@
         <v>4.16666666666667</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>29</v>
+        <v>35</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1" spans="2:10">
+    <row r="9" ht="20" customHeight="1" spans="2:11">
       <c r="B9" s="4">
         <v>46286</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F9" s="5">
         <v>3.2</v>
@@ -1414,75 +1468,84 @@
         <v>3.43333333333333</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>32</v>
+        <v>39</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1" spans="2:10">
-      <c r="B10" s="8">
+    <row r="10" ht="20" customHeight="1" spans="2:11">
+      <c r="B10" s="4">
         <v>46290</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="9">
+      <c r="C10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="5">
         <v>3.8</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="5">
         <v>3.8</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="5">
         <v>4.1</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="7">
         <f t="shared" si="0"/>
         <v>3.9</v>
       </c>
-      <c r="J10" s="11" t="s">
-        <v>36</v>
+      <c r="J10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" spans="2:10">
-      <c r="B11" s="8">
+    <row r="11" ht="20" customHeight="1" spans="2:11">
+      <c r="B11" s="4">
         <v>46294</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="11">
+      <c r="C11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="5">
         <v>4</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="5">
         <v>3.8</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="5">
         <v>4</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="7">
         <f t="shared" si="0"/>
         <v>3.93333333333333</v>
       </c>
-      <c r="J11" s="11" t="s">
-        <v>40</v>
+      <c r="J11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1" spans="2:10">
+    <row r="12" ht="20" customHeight="1" spans="2:11">
       <c r="B12" s="8">
         <v>46298</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="10"/>
@@ -1490,17 +1553,18 @@
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="11" t="e">
-        <f>AVERAGE(F12:H12)</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J12" s="11"/>
+      <c r="K12" s="12"/>
     </row>
-    <row r="13" ht="20" customHeight="1" spans="2:10">
+    <row r="13" ht="20" customHeight="1" spans="2:11">
       <c r="B13" s="8">
         <v>46302</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="10"/>
@@ -1508,10 +1572,11 @@
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="11" t="e">
-        <f>AVERAGE(F13:H13)</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J13" s="11"/>
+      <c r="K13" s="12"/>
     </row>
     <row r="14" ht="20" customHeight="1"/>
     <row r="15" ht="20" customHeight="1"/>

--- a/料力榜.xlsx
+++ b/料力榜.xlsx
@@ -16,6 +16,9 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$K$13</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
   <si>
     <t>日期</t>
   </si>
@@ -72,7 +75,7 @@
     <t>加点滋味</t>
   </si>
   <si>
-    <t>肉蟹煲</t>
+    <t>肉蟹煲料包</t>
   </si>
   <si>
     <t>鲜香微辣，值得一试</t>
@@ -99,7 +102,7 @@
     <t>EP3</t>
   </si>
   <si>
-    <t>芥末小海鲜</t>
+    <t>芥末小海鲜捞汁</t>
   </si>
   <si>
     <t>芥味清爽，略欠鲜香</t>
@@ -111,7 +114,7 @@
     <t>EP4</t>
   </si>
   <si>
-    <t>云南油焖鸡</t>
+    <t>云南油焖鸡料包</t>
   </si>
   <si>
     <t>辣而少香，入味欠佳</t>
@@ -150,7 +153,7 @@
     <t>EP7</t>
   </si>
   <si>
-    <t>牛肉麻婆豆腐</t>
+    <t>牛肉麻婆豆腐料包</t>
   </si>
   <si>
     <t>咸重压味，麻香不足</t>
@@ -165,7 +168,7 @@
     <t>山姆</t>
   </si>
   <si>
-    <t>金汤肥牛</t>
+    <t>金汤肥牛调味料</t>
   </si>
   <si>
     <t>酸辣突出，香味稍弱</t>
@@ -192,7 +195,25 @@
     <t>EP10</t>
   </si>
   <si>
+    <t>沃集鲜</t>
+  </si>
+  <si>
+    <t>党参黄芪骨汤米线</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>药香突出，鸡肉提鲜</t>
+  </si>
+  <si>
     <t>EP11</t>
+  </si>
+  <si>
+    <t>海南鸡饭煮饭料</t>
+  </si>
+  <si>
+    <t>米香油润，鸡鲜味足</t>
   </si>
 </sst>
 </file>
@@ -1205,7 +1226,7 @@
   <cols>
     <col min="2" max="2" width="13.0176991150442" customWidth="1"/>
     <col min="4" max="4" width="10.8318584070796" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7699115044248" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.0619469026549" style="1" customWidth="1"/>
     <col min="6" max="8" width="9" style="1"/>
     <col min="9" max="9" width="12.7964601769912" style="1"/>
     <col min="10" max="10" width="21.5752212389381" customWidth="1"/>
@@ -1541,41 +1562,65 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="2:11">
-      <c r="B12" s="8">
-        <v>46298</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="4">
+        <v>46305</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="11" t="e">
+      <c r="D12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="I12" s="7">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J12" s="11"/>
-      <c r="K12" s="12"/>
+        <v>4.1</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" s="7"/>
     </row>
     <row r="13" ht="20" customHeight="1" spans="2:11">
       <c r="B13" s="8">
-        <v>46302</v>
+        <v>46308</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="11" t="e">
+        <v>56</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="G13" s="9">
+        <v>4</v>
+      </c>
+      <c r="H13" s="9">
+        <v>4.3</v>
+      </c>
+      <c r="I13" s="11">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J13" s="11"/>
+        <v>4.16666666666667</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="K13" s="12"/>
     </row>
     <row r="14" ht="20" customHeight="1"/>
@@ -1585,6 +1630,9 @@
     <row r="18" ht="20" customHeight="1"/>
     <row r="19" ht="20" customHeight="1"/>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B2:K13" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
